--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
@@ -628,7 +628,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>73.53</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H4">
         <v>6.3</v>
@@ -654,7 +654,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -663,10 +663,10 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>76.92</v>
+        <v>77.5</v>
       </c>
       <c r="H5">
         <v>6.3</v>
@@ -817,13 +817,13 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -840,13 +840,13 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1000,7 +1000,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1009,10 +1009,10 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>73.53</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H4">
         <v>6.3</v>
@@ -1026,7 +1026,7 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1035,10 +1035,10 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>76.92</v>
+        <v>77.5</v>
       </c>
       <c r="H5">
         <v>6.4</v>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -82,103 +82,94 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ECHAVARRIA</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>UTRERA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>JOEL MIGUEL</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>ROMINA GISELLE</t>
   </si>
   <si>
     <t>MELANY</t>
   </si>
   <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>ESTRELLA ESMERALDA</t>
+  </si>
+  <si>
+    <t>ESTRELLA RUBI</t>
+  </si>
+  <si>
+    <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>ERICK ANGEL</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
   </si>
 </sst>
 </file>
@@ -628,7 +619,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -637,10 +628,10 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>74.29000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H4">
         <v>6.3</v>
@@ -774,16 +765,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>55.56</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -797,16 +791,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>58.33</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -817,19 +814,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>79.41</v>
+      </c>
+      <c r="H4">
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -843,16 +843,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -866,16 +869,19 @@
         <v>39</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>82.05</v>
+      </c>
+      <c r="H6">
+        <v>6.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -889,16 +895,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>63.33</v>
+      </c>
+      <c r="H7">
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -954,16 +963,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>70.37</v>
+        <v>55.56</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -980,16 +989,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>58.33</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1000,22 +1009,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>74.29000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1032,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>77.5</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1058,16 +1067,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>82.05</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1084,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>50</v>
+        <v>63.33</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,22 +1144,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920030</v>
+        <v>23330051920018</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1158,22 +1167,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920038</v>
+        <v>23330051920024</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1181,22 +1190,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920067</v>
+        <v>23330051920033</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1204,7 +1213,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920072</v>
+        <v>23330051920095</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1213,13 +1222,13 @@
         <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1227,7 +1236,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920083</v>
+        <v>23330051920105</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1236,7 +1245,7 @@
         <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1250,7 +1259,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920105</v>
+        <v>23330051920139</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1259,13 +1268,13 @@
         <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1273,7 +1282,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920112</v>
+        <v>23330051920155</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1282,13 +1291,13 @@
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1296,22 +1305,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920124</v>
+        <v>23330051920154</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1319,22 +1328,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920133</v>
+        <v>23330051920166</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1342,39 +1351,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920255</v>
+        <v>23330051920003</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920099</v>
+        <v>23330051920081</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1383,29 +1392,6 @@
         <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920147</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
@@ -88,9 +88,6 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
     <t>HUERTA</t>
   </si>
   <si>
@@ -106,6 +103,9 @@
     <t>MOLINA</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -118,9 +118,6 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>DURAND</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -145,9 +145,6 @@
     <t>JOEL MIGUEL</t>
   </si>
   <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
     <t>ROMINA GISELLE</t>
   </si>
   <si>
@@ -164,6 +161,9 @@
   </si>
   <si>
     <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
   </si>
   <si>
     <t>ERICK ANGEL</t>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920033</v>
+        <v>23330051920095</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1205,7 +1205,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920095</v>
+        <v>23330051920105</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1236,7 +1236,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920105</v>
+        <v>23330051920139</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1251,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920139</v>
+        <v>23330051920155</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1274,7 +1274,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1282,13 +1282,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920155</v>
+        <v>23330051920154</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>46</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920154</v>
+        <v>23330051920166</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1328,7 +1328,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920166</v>
+        <v>23330051920169</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1380,7 +1380,7 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -82,94 +82,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RAMOS</t>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>UTRERA</t>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>JOEL MIGUEL</t>
-  </si>
-  <si>
-    <t>ROMINA GISELLE</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
-  </si>
-  <si>
-    <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
-    <t>ERICK ANGEL</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
   </si>
 </sst>
 </file>
@@ -963,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>55.56</v>
+        <v>70.37</v>
       </c>
       <c r="H2">
         <v>6.3</v>
@@ -989,13 +944,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>58.33</v>
+        <v>70.83</v>
       </c>
       <c r="H3">
         <v>6.3</v>
@@ -1015,16 +970,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>79.41</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1041,13 +996,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H5">
         <v>6.7</v>
@@ -1067,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>82.05</v>
+        <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1093,16 +1048,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>63.33</v>
+        <v>90</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1144,16 +1099,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920018</v>
+        <v>23330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1167,16 +1122,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920024</v>
+        <v>23330051920025</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1190,22 +1145,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920095</v>
+        <v>23330051920049</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1213,16 +1168,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920105</v>
+        <v>23330051920097</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
         <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1236,162 +1191,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920139</v>
+        <v>23330051920316</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920155</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920154</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920166</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920169</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920003</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920081</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
@@ -927,7 +927,7 @@
         <v>70.37</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -953,7 +953,7 @@
         <v>70.83</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -979,7 +979,7 @@
         <v>82.34999999999999</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1005,7 +1005,7 @@
         <v>90</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1031,7 +1031,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1057,7 +1057,7 @@
         <v>90</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20231.xlsx
@@ -927,7 +927,7 @@
         <v>70.37</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -953,7 +953,7 @@
         <v>70.83</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -979,7 +979,7 @@
         <v>82.34999999999999</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1005,7 +1005,7 @@
         <v>90</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1031,7 +1031,7 @@
         <v>84.62</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1057,7 +1057,7 @@
         <v>90</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
